--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T15:34:05+00:00</t>
+    <t>2026-01-20T16:02:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T16:02:03+00:00</t>
+    <t>2026-01-20T17:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T17:55:30+00:00</t>
+    <t>2026-01-21T09:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T09:01:08+00:00</t>
+    <t>2026-01-21T09:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T09:55:17+00:00</t>
+    <t>2026-01-21T13:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T13:58:49+00:00</t>
+    <t>2026-01-21T14:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T14:06:50+00:00</t>
+    <t>2026-01-21T14:35:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T14:35:59+00:00</t>
+    <t>2026-01-23T08:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T08:59:40+00:00</t>
+    <t>2026-02-03T08:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T08:21:15+00:00</t>
+    <t>2026-02-03T10:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:50:43+00:00</t>
+    <t>2026-02-03T13:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T13:25:15+00:00</t>
+    <t>2026-02-04T07:54:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T07:54:35+00:00</t>
+    <t>2026-02-04T09:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T09:29:46+00:00</t>
+    <t>2026-02-04T11:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:22:34+00:00</t>
+    <t>2026-02-05T10:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T10:48:12+00:00</t>
+    <t>2026-02-05T13:45:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T13:45:20+00:00</t>
+    <t>2026-02-05T14:33:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T14:33:14+00:00</t>
+    <t>2026-02-06T15:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T15:11:45+00:00</t>
+    <t>2026-02-09T15:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T15:38:00+00:00</t>
+    <t>2026-02-10T14:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T14:06:03+00:00</t>
+    <t>2026-02-11T08:41:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T08:41:28+00:00</t>
+    <t>2026-02-11T08:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T08:47:58+00:00</t>
+    <t>2026-02-12T14:05:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:05:06+00:00</t>
+    <t>2026-02-13T15:05:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:05:24+00:00</t>
+    <t>2026-02-13T16:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T16:24:26+00:00</t>
+    <t>2026-02-13T16:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T16:45:56+00:00</t>
+    <t>2026-02-17T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:34:27+00:00</t>
+    <t>2026-02-23T15:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:50:03+00:00</t>
+    <t>2026-02-24T10:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:01:10+00:00</t>
+    <t>2026-02-25T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:11:58+00:00</t>
+    <t>2026-02-26T09:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T09:34:21+00:00</t>
+    <t>2026-02-27T08:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T08:28:09+00:00</t>
+    <t>2026-02-27T09:24:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T09:24:41+00:00</t>
+    <t>2026-02-27T09:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T09:26:51+00:00</t>
+    <t>2026-02-27T09:31:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T09:31:51+00:00</t>
+    <t>2026-02-27T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:14:27+00:00</t>
+    <t>2026-03-02T14:14:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T14:14:24+00:00</t>
+    <t>2026-03-10T12:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:57:18+00:00</t>
+    <t>2026-03-10T13:12:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T13:12:33+00:00</t>
+    <t>2026-03-18T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T14:29:18+00:00</t>
+    <t>2026-03-19T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T08:56:44+00:00</t>
+    <t>2026-03-23T13:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:01:42+00:00</t>
+    <t>2026-03-24T16:53:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3771" uniqueCount="511">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T16:53:46+00:00</t>
+    <t>2026-03-26T15:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/QuestionnaireResponse|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/QuestionnaireResponse</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -273,7 +273,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}auto-eval-porteur:Dans le cas d'une auto évaluation, le porteur doit être renseigné. {(source.exists() and source.reference.contains('Patient/')) implies extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-qr-participant').extension.where(url='TDDUIHolder').exists()}professionnel-requis:Hormis le cas de l'auto évaluation, au moins un des 3 éléments (Evaluateur, Responsable, Auteur) doit être renseigné {source.reference.contains('Patient/').not() implies (source.reference.contains('Practitioner/') or author.exists() or extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-qr-participant').extension.where(url='TDDUIResponsible').exists())}</t>
   </si>
   <si>
     <t>Evaluation AGGIR PA SSIAD, Evaluation AGGIR PH SSIAD</t>
@@ -630,14 +630,14 @@
     <t>TDDUIQRParticipant</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-qr-participant|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-qr-participant}
 </t>
   </si>
   <si>
-    <t>Responsable et auteur du statut de l'évaluation</t>
-  </si>
-  <si>
-    <t>Extension permettant d'ajouter le responsable de l'évaluation et l'auteur du statut de l'évaluation dans un QuestionnaireResponse.</t>
+    <t>TDDUI QR Participant</t>
+  </si>
+  <si>
+    <t>Extension permettant d'ajouter le responsable et le porteur de l'évaluation dans un QuestionnaireResponse.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -701,7 +701,7 @@
     <t>QuestionnaireResponse.extension.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner)
 </t>
   </si>
   <si>
@@ -714,25 +714,29 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIStatusAuthor</t>
-  </si>
-  <si>
-    <t>TDDUIStatusAuthor</t>
-  </si>
-  <si>
-    <t>Statut.auteur</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIStatusAuthor.id</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIStatusAuthor.extension</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIStatusAuthor.url</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIStatusAuthor.value[x]</t>
+    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIHolder</t>
+  </si>
+  <si>
+    <t>TDDUIHolder</t>
+  </si>
+  <si>
+    <t>Porteur</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIHolder.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIHolder.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIHolder.url</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:TDDUIQRParticipant.extension:TDDUIHolder.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
+</t>
   </si>
   <si>
     <t>QuestionnaireResponse.extension:TDDUIQRParticipant.url</t>
@@ -760,11 +764,11 @@
     <t>TDDUIAttachment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment}
 </t>
   </si>
   <si>
-    <t>Pièce jointe</t>
+    <t>TDDUI Attachment</t>
   </si>
   <si>
     <t>Extension permettant de véhiculer des pièces jointes que ce soit pour l'évaluation, l'évènement ou le projet personnalisé. L'extension référence le profil PDSm_SimplifiedPublish.</t>
@@ -779,11 +783,11 @@
     <t>TDDUIComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment}
 </t>
   </si>
   <si>
-    <t>Commentaire</t>
+    <t>TDDUI Comment</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -796,6 +800,25 @@
     <t>commentaireEvaluation</t>
   </si>
   <si>
+    <t>QuestionnaireResponse.extension:TDDUIAssessmentMethod</t>
+  </si>
+  <si>
+    <t>TDDUIAssessmentMethod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-assessment-method}
+</t>
+  </si>
+  <si>
+    <t>TDDUI Assessment Method</t>
+  </si>
+  <si>
+    <t>Mode d'évaluation, texte libre permettant de mettre le contexte de l'évaluation.</t>
+  </si>
+  <si>
+    <t>modaliteEvaluation</t>
+  </si>
+  <si>
     <t>QuestionnaireResponse.modifierExtension</t>
   </si>
   <si>
@@ -1110,6 +1133,46 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>QuestionnaireResponse.status.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.status.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.status.extension:TDDUIStatusAuthor</t>
+  </si>
+  <si>
+    <t>TDDUIStatusAuthor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author}
+</t>
+  </si>
+  <si>
+    <t>TDDUI Status Author</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter l'auteur du statut.</t>
+  </si>
+  <si>
+    <t>Statut.auteur</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.status.value</t>
+  </si>
+  <si>
+    <t>Primitive value for code</t>
+  </si>
+  <si>
+    <t>string.value</t>
+  </si>
+  <si>
     <t>QuestionnaireResponse.subject</t>
   </si>
   <si>
@@ -1117,7 +1180,7 @@
 Focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1148,7 +1211,7 @@
     <t>QuestionnaireResponse.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-evenement|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-evenement)
 </t>
   </si>
   <si>
@@ -1244,6 +1307,10 @@
   </si>
   <si>
     <t>QuestionnaireResponse.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
+</t>
   </si>
   <si>
     <t>The person who answered the questions</t>
@@ -1842,12 +1909,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO96"/>
+  <dimension ref="A1:AO101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="75.4765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="52.62890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="21.21484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="40.65625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -5296,7 +5363,7 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>222</v>
@@ -5385,10 +5452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5428,7 +5495,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>80</v>
@@ -5502,10 +5569,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5528,7 +5595,7 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>222</v>
@@ -5617,13 +5684,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>80</v>
@@ -5645,13 +5712,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5717,10 +5784,10 @@
         <v>120</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -5734,13 +5801,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -5762,13 +5829,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5834,10 +5901,10 @@
         <v>120</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
@@ -5851,46 +5918,44 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>112</v>
+        <v>253</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5938,7 +6003,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5947,22 +6012,22 @@
         <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -5970,43 +6035,45 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>256</v>
+        <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6055,42 +6122,42 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>262</v>
+        <v>191</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6098,7 +6165,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>91</v>
@@ -6110,19 +6177,21 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>105</v>
+        <v>263</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>106</v>
+        <v>264</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>107</v>
+        <v>265</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6170,7 +6239,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>108</v>
+        <v>262</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6182,41 +6251,41 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>109</v>
+        <v>269</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6228,17 +6297,15 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6275,31 +6342,31 @@
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6319,46 +6386,44 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>268</v>
+        <v>114</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6382,43 +6447,43 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>274</v>
+        <v>119</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6430,7 +6495,7 @@
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>275</v>
+        <v>109</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6438,10 +6503,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6458,25 +6523,25 @@
         <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6501,13 +6566,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>150</v>
+        <v>278</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6525,7 +6590,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6549,7 +6614,7 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6557,10 +6622,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6568,7 +6633,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -6583,19 +6648,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>284</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6605,46 +6670,46 @@
         <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="T41" t="s" s="2">
+      <c r="AA41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6668,7 +6733,7 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -6676,10 +6741,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6702,18 +6767,20 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6722,7 +6789,7 @@
         <v>80</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>298</v>
@@ -6804,7 +6871,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -6819,15 +6886,17 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6840,7 +6909,7 @@
         <v>80</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>80</v>
@@ -6876,7 +6945,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6900,7 +6969,7 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -6908,10 +6977,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6934,17 +7003,15 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N44" t="s" s="2">
         <v>311</v>
       </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7032,14 +7099,14 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7051,18 +7118,18 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7110,13 +7177,13 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
@@ -7131,10 +7198,10 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7142,14 +7209,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7176,10 +7243,10 @@
       <c r="M46" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7227,7 +7294,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7266,14 +7333,14 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>80</v>
@@ -7285,20 +7352,18 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N47" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7352,7 +7417,7 @@
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
@@ -7361,16 +7426,16 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7378,14 +7443,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7398,25 +7463,25 @@
         <v>80</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>168</v>
+        <v>338</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7441,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>344</v>
+        <v>80</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>345</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7465,10 +7530,10 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>91</v>
@@ -7480,31 +7545,31 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>349</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7517,25 +7582,25 @@
         <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>352</v>
+        <v>168</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7560,13 +7625,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7584,10 +7649,10 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>91</v>
@@ -7599,27 +7664,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7639,23 +7704,19 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7703,7 +7764,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>361</v>
+        <v>108</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7715,41 +7776,41 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>369</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>370</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7758,23 +7819,19 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>112</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>193</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7810,58 +7867,58 @@
         <v>80</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>371</v>
+        <v>119</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="D52" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7877,23 +7934,19 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>221</v>
+        <v>363</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -7941,42 +7994,42 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>119</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>389</v>
+        <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>391</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7996,23 +8049,19 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8060,7 +8109,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8072,41 +8121,41 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>398</v>
+        <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>399</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>91</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -8115,21 +8164,23 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8177,42 +8228,42 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>405</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>80</v>
+        <v>377</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>407</v>
+        <v>379</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8232,19 +8283,23 @@
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>105</v>
+        <v>382</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>106</v>
+        <v>383</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8292,7 +8347,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>108</v>
+        <v>381</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8304,41 +8359,41 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>80</v>
+        <v>388</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>109</v>
+        <v>389</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>80</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
@@ -8347,19 +8402,23 @@
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>112</v>
+        <v>393</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>193</v>
+        <v>394</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8395,58 +8454,58 @@
         <v>80</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC56" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>119</v>
+        <v>391</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>80</v>
+        <v>398</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>80</v>
+        <v>398</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>80</v>
+        <v>399</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8462,19 +8521,23 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>247</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8522,34 +8585,34 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>119</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="58">
@@ -8561,26 +8624,26 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>112</v>
+        <v>413</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>414</v>
@@ -8589,10 +8652,10 @@
         <v>415</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>115</v>
+        <v>416</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>253</v>
+        <v>417</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8641,42 +8704,42 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>80</v>
+        <v>418</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>80</v>
+        <v>418</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>191</v>
+        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8687,7 +8750,7 @@
         <v>91</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8699,18 +8762,18 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>105</v>
+        <v>422</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8758,31 +8821,31 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>426</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -8790,10 +8853,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8816,20 +8879,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>106</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8877,7 +8936,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>423</v>
+        <v>108</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8889,7 +8948,7 @@
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
@@ -8901,7 +8960,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>428</v>
+        <v>109</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -8909,10 +8968,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8923,7 +8982,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -8935,18 +8994,16 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>430</v>
+        <v>193</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8982,31 +9039,29 @@
         <v>80</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>429</v>
+        <v>119</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
@@ -9018,7 +9073,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9026,12 +9081,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9040,7 +9097,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -9052,17 +9109,15 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>401</v>
+        <v>247</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>435</v>
+        <v>248</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9111,7 +9166,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>434</v>
+        <v>119</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9120,22 +9175,22 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9143,42 +9198,46 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>80</v>
+        <v>434</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>106</v>
+        <v>435</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9226,19 +9285,19 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>108</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9250,7 +9309,7 @@
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9258,21 +9317,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
@@ -9284,18 +9343,18 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>113</v>
+        <v>439</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9343,31 +9402,31 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>119</v>
+        <v>438</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>109</v>
+        <v>443</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9375,45 +9434,45 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>115</v>
+        <v>447</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>253</v>
+        <v>448</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9462,19 +9521,19 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
@@ -9486,7 +9545,7 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>191</v>
+        <v>449</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -9494,10 +9553,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9520,19 +9579,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>445</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9557,31 +9614,31 @@
         <v>80</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9605,7 +9662,7 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -9613,10 +9670,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9639,18 +9696,18 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
       </c>
@@ -9698,7 +9755,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9713,16 +9770,16 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>407</v>
+        <v>461</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -9730,10 +9787,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9744,7 +9801,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>80</v>
@@ -9756,18 +9813,16 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>401</v>
+        <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>458</v>
+        <v>106</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>459</v>
+        <v>107</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -9815,22 +9870,22 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>457</v>
+        <v>108</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>406</v>
+        <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
@@ -9839,7 +9894,7 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>407</v>
+        <v>109</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -9847,21 +9902,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -9873,15 +9928,17 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -9930,19 +9987,19 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
@@ -9962,14 +10019,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>80</v>
+        <v>434</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9982,22 +10039,26 @@
         <v>80</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>193</v>
+        <v>435</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10033,17 +10094,19 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC70" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>119</v>
+        <v>437</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10067,7 +10130,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10075,14 +10138,12 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10103,16 +10164,20 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>246</v>
+        <v>466</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>247</v>
+        <v>467</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10136,13 +10201,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>80</v>
+        <v>471</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10160,22 +10225,22 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>119</v>
+        <v>465</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>80</v>
@@ -10184,7 +10249,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10192,14 +10257,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10212,25 +10277,23 @@
         <v>80</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>253</v>
+        <v>477</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -10279,7 +10342,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>416</v>
+        <v>474</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10291,7 +10354,7 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
@@ -10303,7 +10366,7 @@
         <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>191</v>
+        <v>428</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -10311,10 +10374,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10322,10 +10385,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>80</v>
@@ -10337,17 +10400,17 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>105</v>
+        <v>422</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>418</v>
+        <v>479</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>420</v>
+        <v>481</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -10396,13 +10459,13 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>417</v>
+        <v>478</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>80</v>
@@ -10411,7 +10474,7 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
@@ -10420,7 +10483,7 @@
         <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10428,10 +10491,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10454,20 +10517,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>424</v>
+        <v>106</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
       </c>
@@ -10515,7 +10574,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>423</v>
+        <v>108</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10527,7 +10586,7 @@
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
@@ -10539,7 +10598,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>428</v>
+        <v>109</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10547,10 +10606,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10561,7 +10620,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>80</v>
@@ -10573,18 +10632,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>430</v>
+        <v>193</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>80</v>
       </c>
@@ -10620,31 +10677,29 @@
         <v>80</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>429</v>
+        <v>119</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -10656,7 +10711,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -10664,12 +10719,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="D76" t="s" s="2">
         <v>80</v>
       </c>
@@ -10678,7 +10735,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>80</v>
@@ -10690,17 +10747,15 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>401</v>
+        <v>247</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>435</v>
+        <v>248</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -10749,7 +10804,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>434</v>
+        <v>119</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10758,13 +10813,13 @@
         <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>80</v>
@@ -10773,7 +10828,7 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -10781,42 +10836,46 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>80</v>
+        <v>434</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>106</v>
+        <v>435</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -10864,19 +10923,19 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>108</v>
+        <v>437</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
@@ -10888,7 +10947,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -10896,21 +10955,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -10922,18 +10981,18 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>113</v>
+        <v>439</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -10981,22 +11040,22 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>119</v>
+        <v>438</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>80</v>
@@ -11005,7 +11064,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>109</v>
+        <v>443</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11013,45 +11072,45 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>115</v>
+        <v>447</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>253</v>
+        <v>448</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11100,19 +11159,19 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11124,7 +11183,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>191</v>
+        <v>449</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11132,10 +11191,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11158,19 +11217,17 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>445</v>
+        <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11195,31 +11252,31 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11243,7 +11300,7 @@
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -11251,10 +11308,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11277,18 +11334,18 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11336,7 +11393,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11351,7 +11408,7 @@
         <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11360,7 +11417,7 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>407</v>
+        <v>461</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -11368,10 +11425,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11382,7 +11439,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11394,18 +11451,16 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>401</v>
+        <v>105</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>458</v>
+        <v>106</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>459</v>
+        <v>107</v>
       </c>
       <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11453,22 +11508,22 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>457</v>
+        <v>108</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>80</v>
@@ -11477,7 +11532,7 @@
         <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>407</v>
+        <v>109</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -11485,21 +11540,21 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -11511,15 +11566,17 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -11568,19 +11625,19 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -11600,14 +11657,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>80</v>
+        <v>434</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11620,22 +11677,26 @@
         <v>80</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>193</v>
+        <v>435</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
       </c>
@@ -11671,17 +11732,19 @@
         <v>80</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC84" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>119</v>
+        <v>437</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11705,7 +11768,7 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -11713,14 +11776,12 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>80</v>
       </c>
@@ -11741,16 +11802,20 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>246</v>
+        <v>466</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>247</v>
+        <v>467</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -11774,13 +11839,13 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>80</v>
+        <v>471</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -11798,22 +11863,22 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>119</v>
+        <v>465</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>80</v>
@@ -11822,7 +11887,7 @@
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -11830,14 +11895,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11850,25 +11915,23 @@
         <v>80</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>253</v>
+        <v>477</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -11917,7 +11980,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>416</v>
+        <v>474</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11929,7 +11992,7 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
@@ -11941,7 +12004,7 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>191</v>
+        <v>428</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -11949,10 +12012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11960,10 +12023,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -11975,17 +12038,17 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>105</v>
+        <v>422</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>418</v>
+        <v>479</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>420</v>
+        <v>481</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12034,13 +12097,13 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>417</v>
+        <v>478</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>80</v>
@@ -12049,7 +12112,7 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>421</v>
+        <v>496</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>80</v>
@@ -12058,7 +12121,7 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -12066,10 +12129,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12092,20 +12155,16 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>424</v>
+        <v>106</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
       </c>
@@ -12153,7 +12212,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>423</v>
+        <v>108</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12165,7 +12224,7 @@
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
@@ -12177,7 +12236,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>428</v>
+        <v>109</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -12185,10 +12244,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12199,7 +12258,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -12211,18 +12270,16 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>430</v>
+        <v>193</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -12258,31 +12315,29 @@
         <v>80</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>429</v>
+        <v>119</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>80</v>
@@ -12294,7 +12349,7 @@
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -12302,12 +12357,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="D90" t="s" s="2">
         <v>80</v>
       </c>
@@ -12316,7 +12373,7 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>80</v>
@@ -12328,17 +12385,15 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>401</v>
+        <v>247</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>435</v>
+        <v>248</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -12387,7 +12442,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>434</v>
+        <v>119</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12396,13 +12451,13 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>80</v>
@@ -12411,7 +12466,7 @@
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -12419,42 +12474,46 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>80</v>
+        <v>434</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>106</v>
+        <v>435</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -12502,19 +12561,19 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>108</v>
+        <v>437</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
@@ -12526,7 +12585,7 @@
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -12534,21 +12593,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>80</v>
@@ -12560,18 +12619,18 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>113</v>
+        <v>439</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
       </c>
@@ -12619,22 +12678,22 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>119</v>
+        <v>438</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>80</v>
@@ -12643,7 +12702,7 @@
         <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>109</v>
+        <v>443</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -12651,45 +12710,45 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>115</v>
+        <v>447</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>253</v>
+        <v>448</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -12738,19 +12797,19 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>80</v>
@@ -12762,7 +12821,7 @@
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>191</v>
+        <v>449</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -12770,10 +12829,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12796,19 +12855,17 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>445</v>
+        <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -12833,31 +12890,31 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12881,7 +12938,7 @@
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -12889,10 +12946,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12915,18 +12972,18 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -12974,7 +13031,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12989,7 +13046,7 @@
         <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>80</v>
@@ -12998,7 +13055,7 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>407</v>
+        <v>461</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13006,10 +13063,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13020,7 +13077,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>80</v>
@@ -13032,18 +13089,16 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>458</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>459</v>
+        <v>107</v>
       </c>
       <c r="N96" s="2"/>
-      <c r="O96" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>80</v>
       </c>
@@ -13091,33 +13146,622 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>457</v>
+        <v>108</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
+      <c r="H97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO96" t="s" s="2">
+      <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AO101" t="s" s="2">
         <v>80</v>
       </c>
     </row>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T15:00:26+00:00</t>
+    <t>2026-03-31T13:26:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T13:26:33+00:00</t>
+    <t>2026-04-09T09:14:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:14:18+00:00</t>
+    <t>2026-04-09T09:18:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:18:02+00:00</t>
+    <t>2026-04-24T09:04:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
